--- a/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFIconSet.xlsx
+++ b/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFIconSet.xlsx
@@ -360,29 +360,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="0">
+      <x:c r="A1">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="0">
+      <x:c r="A2">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="0">
+      <x:c r="A3">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -390,16 +387,12 @@
   <x:conditionalFormatting sqref="A1:A4">
     <x:cfRule type="iconSet" priority="1">
       <x:iconSet iconSet="3TrafficLights2" showValue="0" reverse="1">
-        <x:cfvo type="num" val="0" gte="1"/>
-        <x:cfvo type="num" val="2" gte="1"/>
-        <x:cfvo type="num" val="3" gte="1"/>
+        <x:cfvo type="num" val="0"/>
+        <x:cfvo type="num" val="2"/>
+        <x:cfvo type="num" val="3"/>
       </x:iconSet>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>